--- a/src/assets/市院、区县院各级部门表(1)(2)(1)2018727.xlsx
+++ b/src/assets/市院、区县院各级部门表(1)(2)(1)2018727.xlsx
@@ -370,88 +370,20 @@
 http://www.huaian.he.jcy/hamxb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案管部
-http://www.huaian.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/haagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>刑事执行检察部
-http://www.huaian.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/haxzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公诉部
-http://www.huaian.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hagsb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合保障部
-http://www.huaian.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hazhbzb</t>
-    </r>
+    <t>案管部
+http://www.huaian.he.jcy/haagb</t>
+  </si>
+  <si>
+    <t>刑事执行检察部
+http://www.huaian.he.jcy/haxzb</t>
+  </si>
+  <si>
+    <t>公诉部
+http://www.huaian.he.jcy/hagsb</t>
+  </si>
+  <si>
+    <t>综合保障部
+http://www.huaian.he.jcy/hazhbzb</t>
   </si>
   <si>
     <t>下花园</t>
@@ -465,88 +397,20 @@
 http://www.zjkxhy.he.jcy/xhyxzb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合业务检察部
-http://www.zjkxhy.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhyzhywb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.zjkxhy.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhymxb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案件管理检察部
-http://www.zjkxhy.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhyagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>检务保障部
-http://www.zjkxhy.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhyjwbzb</t>
-    </r>
+    <t>综合业务检察部
+http://www.zjkxhy.he.jcy/xhyzhywb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.zjkxhy.he.jcy/xhymxb</t>
+  </si>
+  <si>
+    <t>案件管理检察部
+http://www.zjkxhy.he.jcy/xhyagb</t>
+  </si>
+  <si>
+    <t>检务保障部
+http://www.zjkxhy.he.jcy/xhyjwbzb</t>
   </si>
   <si>
     <t>经开区</t>
@@ -560,88 +424,20 @@
 http://www.zjkjk.he.jcy/jkzhbzb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案件管理部
-http://www.zjkjk.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/jkagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公诉部
-http://www.zjkjk.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/jkgsb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>侦查监督部
-http://www.zjkjk.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/jkzjb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.zjkjk.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/jkmxb</t>
-    </r>
+    <t>案件管理部
+http://www.zjkjk.he.jcy/jkagb</t>
+  </si>
+  <si>
+    <t>公诉部
+http://www.zjkjk.he.jcy/jkgsb</t>
+  </si>
+  <si>
+    <t>侦查监督部
+http://www.zjkjk.he.jcy/jkzjb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.zjkjk.he.jcy/jkmxb</t>
   </si>
   <si>
     <t>涿鹿</t>
@@ -655,88 +451,20 @@
 http://www.zhuolu.he.jcy/zljwbzb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>政治部
-http://www.zhuolu.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/zlzzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案件管理部
-http://www.zhuolu.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/zlagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>刑事检察部
-http://www.zhuolu.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/zlxzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.zhuolu.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/zlmxb</t>
-    </r>
+    <t>政治部
+http://www.zhuolu.he.jcy/zlzzb</t>
+  </si>
+  <si>
+    <t>案件管理部
+http://www.zhuolu.he.jcy/zlagb</t>
+  </si>
+  <si>
+    <t>刑事检察部
+http://www.zhuolu.he.jcy/zlxzb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.zhuolu.he.jcy/zlmxb</t>
   </si>
   <si>
     <t>怀来</t>
@@ -750,151 +478,32 @@
 http://www.huailai.he.jcy/hlgsb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>侦查监督部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlzjb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案件管理检察部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlmxb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>未成年人检察部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlwjb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>刑事执行检察部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlxzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>控告申诉检察部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlksb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合保障部
-http://www.huailai.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/hlzhbzb</t>
-    </r>
+    <t>侦查监督部
+http://www.huailai.he.jcy/hlzjb</t>
+  </si>
+  <si>
+    <t>案件管理检察部
+http://www.huailai.he.jcy/hlagb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.huailai.he.jcy/hlmxb</t>
+  </si>
+  <si>
+    <t>未成年人检察部
+http://www.huailai.he.jcy/hlwjb</t>
+  </si>
+  <si>
+    <t>刑事执行检察部
+http://www.huailai.he.jcy/hlxzb</t>
+  </si>
+  <si>
+    <t>控告申诉检察部
+http://www.huailai.he.jcy/hlksb</t>
+  </si>
+  <si>
+    <t>综合保障部
+http://www.huailai.he.jcy/hlzhbzb</t>
   </si>
   <si>
     <t>万全</t>
@@ -908,91 +517,23 @@
 http://www.zjkwq.he.jcy/wqzjb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公诉部
-http://www.zjkwq.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/wqgsb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.zjkwq.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/wqmxb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案件管理部
-http://www.zjkwq.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/wqagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合保障部
-http://www.zjkwq.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/wqzhbzb</t>
-    </r>
-  </si>
-  <si>
-    <t>宣化</t>
+    <t>公诉部
+http://www.zjkwq.he.jcy/wqgsb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.zjkwq.he.jcy/wqmxb</t>
+  </si>
+  <si>
+    <t>案件管理部 MM
+http://www.zjkwq.he.jcy/wqagb</t>
+  </si>
+  <si>
+    <t>综合保障部
+http://www.zjkwq.he.jcy/wqzhbzb</t>
+  </si>
+  <si>
+    <t>宣化M</t>
   </si>
   <si>
     <t>专项活动
@@ -1434,10 +975,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1469,9 +1010,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1499,14 +1047,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -1516,6 +1056,29 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1545,36 +1108,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -1591,6 +1124,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="等线"/>
@@ -1600,7 +1134,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1615,6 +1156,144 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1627,49 +1306,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1682,120 +1337,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1851,6 +1392,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -1861,15 +1426,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1889,26 +1445,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1932,31 +1488,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1965,131 +1506,131 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2427,7 +1968,8 @@
   <sheetFormatPr defaultColWidth="8.58333333333333" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6.75" style="3" customWidth="1"/>
-    <col min="2" max="3" width="28.8333333333333" style="3" customWidth="1"/>
+    <col min="2" max="2" width="28.8333333333333" style="3" customWidth="1"/>
+    <col min="3" max="3" width="27.875" style="3" customWidth="1"/>
     <col min="4" max="4" width="31.5833333333333" style="3" customWidth="1"/>
     <col min="5" max="5" width="31.0833333333333" style="3" customWidth="1"/>
     <col min="6" max="6" width="29.25" style="3" customWidth="1"/>

--- a/src/assets/市院、区县院各级部门表(1)(2)(1)2018727.xlsx
+++ b/src/assets/市院、区县院各级部门表(1)(2)(1)2018727.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20385" windowHeight="8520"/>
+    <workbookView windowWidth="20385" windowHeight="8520" tabRatio="393"/>
   </bookViews>
   <sheets>
     <sheet name="县区院" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
     <t>康保</t>
   </si>
   <si>
-    <t>专项活动
+    <t>专项活动 X
 http://www.kangbao.he.jcy/kbzxhd</t>
   </si>
   <si>
@@ -168,8 +168,8 @@
 http://www.kangbao.he.jcy/kbmx</t>
   </si>
   <si>
-    <t>公诉部 X
-http://www.kangbao.he.jcy/zhgs</t>
+    <t>公诉部 
+http://www.kangbao.he.jcy/kbgs</t>
   </si>
   <si>
     <t>综合保障部
@@ -544,172 +544,36 @@
 http://www.zjkxh.he.jcy/xhzjb</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>公诉部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhgsb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>民事行政检察部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhmxb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">刑事执行检察部
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>http://www.zjkxh.he.jcy/xhxzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>未成年刑事检察部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhwjb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>刑事审查监督检察部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhxsscjdb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>案管部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhagb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>政治部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhzzb</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>检察事务管理部
-http://www.zjkxh.he.jcy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="等线"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>/xhjcswglb</t>
-    </r>
+    <t>公诉部
+http://www.zjkxh.he.jcy/xhgsb</t>
+  </si>
+  <si>
+    <t>民事行政检察部
+http://www.zjkxh.he.jcy/xhmxb</t>
+  </si>
+  <si>
+    <t>刑事执行检察部
+http://www.zjkxh.he.jcy/xhxzb</t>
+  </si>
+  <si>
+    <t>未成年刑事检察部
+http://www.zjkxh.he.jcy/xhwjb</t>
+  </si>
+  <si>
+    <t>刑事审查监督检察部
+http://www.zjkxh.he.jcy/xhxsscjdb</t>
+  </si>
+  <si>
+    <t>案管部
+http://www.zjkxh.he.jcy/xhagb</t>
+  </si>
+  <si>
+    <t>政治部
+http://www.zjkxh.he.jcy/xhzzb</t>
+  </si>
+  <si>
+    <t>检察事务管理部
+http://www.zjkxh.he.jcy/xhjcswglb</t>
   </si>
   <si>
     <r>
@@ -976,9 +840,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1004,6 +868,51 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="等线"/>
       <charset val="0"/>
@@ -1017,36 +926,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="等线"/>
@@ -1055,14 +934,46 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1085,42 +996,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1131,21 +1010,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1156,19 +1020,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1180,49 +1152,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1234,109 +1194,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1392,6 +1256,65 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -1415,36 +1338,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1459,45 +1352,16 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1506,131 +1370,131 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="23" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
